--- a/tablas-de-mortalidad/tarea-inegi-tablas-transversales/fuentes/Fuentes_de_consulta.xlsx
+++ b/tablas-de-mortalidad/tarea-inegi-tablas-transversales/fuentes/Fuentes_de_consulta.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alumnouaemex-my.sharepoint.com/personal/mlrsvenegasg_ext_uaemex_mx/Documents/Documents/UAEM_2026/D/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spart\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4196939B-44AF-4C89-9A7C-9818B4E420EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698443EC-5440-48BB-A2A1-8AA1722C3C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{89C60A90-0A37-4FC4-970E-583EC7A63EDC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{89C60A90-0A37-4FC4-970E-583EC7A63EDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Fuentes de datos" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -391,8 +392,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="##"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="##"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -627,22 +628,46 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -656,30 +681,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -899,9 +900,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -939,7 +940,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1045,7 +1046,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1187,7 +1188,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1198,646 +1199,646 @@
   <dimension ref="B2:U127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="2"/>
-    <col min="2" max="2" width="22.28515625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="11.42578125" style="2"/>
-    <col min="5" max="5" width="23.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="11.42578125" style="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="11.42578125" style="1"/>
+    <col min="5" max="5" width="23.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
     </row>
     <row r="3" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
     </row>
     <row r="4" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
     </row>
     <row r="6" spans="2:21" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
     </row>
     <row r="7" spans="2:21" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="10" t="s">
+      <c r="G35" s="19"/>
+      <c r="H35" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="I35" s="11"/>
+      <c r="I35" s="21"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="14" t="s">
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="G36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H36" s="15" t="s">
+      <c r="H36" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I36" s="16" t="s">
+      <c r="I36" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="8">
         <v>7569573</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F37" s="8">
         <v>3741386</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="8">
         <v>49.426645000000001</v>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="8">
         <v>3828187</v>
       </c>
-      <c r="I37" s="17">
+      <c r="I37" s="8">
         <v>50.573354999999999</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="10">
         <v>9669960</v>
       </c>
-      <c r="F38" s="19">
+      <c r="F38" s="10">
         <v>4785294</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="10">
         <v>49.486181999999999</v>
       </c>
-      <c r="H38" s="19">
+      <c r="H38" s="10">
         <v>4884666</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="10">
         <v>50.513818000000001</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E39" s="19">
+      <c r="E39" s="10">
         <v>10885388</v>
       </c>
-      <c r="F39" s="19">
+      <c r="F39" s="10">
         <v>5353603</v>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="10">
         <v>49.181553999999998</v>
       </c>
-      <c r="H39" s="19">
+      <c r="H39" s="10">
         <v>5531785</v>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="10">
         <v>50.818446000000002</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E40" s="19">
+      <c r="E40" s="10">
         <v>10833608</v>
       </c>
-      <c r="F40" s="19">
+      <c r="F40" s="10">
         <v>5349921</v>
       </c>
-      <c r="G40" s="19">
+      <c r="G40" s="10">
         <v>49.382634000000003</v>
       </c>
-      <c r="H40" s="19">
+      <c r="H40" s="10">
         <v>5483687</v>
       </c>
-      <c r="I40" s="19">
+      <c r="I40" s="10">
         <v>50.617365999999997</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E41" s="19">
+      <c r="E41" s="10">
         <v>10360929</v>
       </c>
-      <c r="F41" s="19">
+      <c r="F41" s="10">
         <v>5319788</v>
       </c>
-      <c r="G41" s="19">
+      <c r="G41" s="10">
         <v>51.344701000000001</v>
       </c>
-      <c r="H41" s="19">
+      <c r="H41" s="10">
         <v>5041141</v>
       </c>
-      <c r="I41" s="19">
+      <c r="I41" s="10">
         <v>48.655298999999999</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E42" s="19">
+      <c r="E42" s="10">
         <v>9810773</v>
       </c>
-      <c r="F42" s="19">
+      <c r="F42" s="10">
         <v>5104330</v>
       </c>
-      <c r="G42" s="19">
+      <c r="G42" s="10">
         <v>52.027807000000003</v>
       </c>
-      <c r="H42" s="19">
+      <c r="H42" s="10">
         <v>4706443</v>
       </c>
-      <c r="I42" s="19">
+      <c r="I42" s="10">
         <v>47.972192999999997</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E43" s="19">
+      <c r="E43" s="10">
         <v>10027553</v>
       </c>
-      <c r="F43" s="19">
+      <c r="F43" s="10">
         <v>5282566</v>
       </c>
-      <c r="G43" s="19">
+      <c r="G43" s="10">
         <v>52.680509000000001</v>
       </c>
-      <c r="H43" s="19">
+      <c r="H43" s="10">
         <v>4744987</v>
       </c>
-      <c r="I43" s="19">
+      <c r="I43" s="10">
         <v>47.319490999999999</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E44" s="19">
+      <c r="E44" s="10">
         <v>9620908</v>
       </c>
-      <c r="F44" s="19">
+      <c r="F44" s="10">
         <v>5095386</v>
       </c>
-      <c r="G44" s="19">
+      <c r="G44" s="10">
         <v>52.961592000000003</v>
       </c>
-      <c r="H44" s="19">
+      <c r="H44" s="10">
         <v>4525522</v>
       </c>
-      <c r="I44" s="19">
+      <c r="I44" s="10">
         <v>47.038407999999997</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E45" s="19">
+      <c r="E45" s="10">
         <v>8974041</v>
       </c>
-      <c r="F45" s="19">
+      <c r="F45" s="10">
         <v>4742766</v>
       </c>
-      <c r="G45" s="19">
+      <c r="G45" s="10">
         <v>52.849837000000001</v>
       </c>
-      <c r="H45" s="19">
+      <c r="H45" s="10">
         <v>4231275</v>
       </c>
-      <c r="I45" s="19">
+      <c r="I45" s="10">
         <v>47.150162999999999</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E46" s="19">
+      <c r="E46" s="10">
         <v>8374000</v>
       </c>
-      <c r="F46" s="19">
+      <c r="F46" s="10">
         <v>4437822</v>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="10">
         <v>52.995246999999999</v>
       </c>
-      <c r="H46" s="19">
+      <c r="H46" s="10">
         <v>3936178</v>
       </c>
-      <c r="I46" s="19">
+      <c r="I46" s="10">
         <v>47.004753000000001</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E47" s="19">
+      <c r="E47" s="10">
         <v>8352139</v>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="10">
         <v>4409290</v>
       </c>
-      <c r="G47" s="19">
+      <c r="G47" s="10">
         <v>52.792344999999997</v>
       </c>
-      <c r="H47" s="19">
+      <c r="H47" s="10">
         <v>3942849</v>
       </c>
-      <c r="I47" s="19">
+      <c r="I47" s="10">
         <v>47.207655000000003</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="D48" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E48" s="19">
+      <c r="E48" s="10">
         <v>6709847</v>
       </c>
-      <c r="F48" s="19">
+      <c r="F48" s="10">
         <v>3553454</v>
       </c>
-      <c r="G48" s="19">
+      <c r="G48" s="10">
         <v>52.958793</v>
       </c>
-      <c r="H48" s="19">
+      <c r="H48" s="10">
         <v>3156393</v>
       </c>
-      <c r="I48" s="19">
+      <c r="I48" s="10">
         <v>47.041207</v>
       </c>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E49" s="19">
+      <c r="E49" s="10">
         <v>5991546</v>
       </c>
-      <c r="F49" s="19">
+      <c r="F49" s="10">
         <v>3257527</v>
       </c>
-      <c r="G49" s="19">
+      <c r="G49" s="10">
         <v>54.368721999999998</v>
       </c>
-      <c r="H49" s="19">
+      <c r="H49" s="10">
         <v>2734019</v>
       </c>
-      <c r="I49" s="19">
+      <c r="I49" s="10">
         <v>45.631278000000002</v>
       </c>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E50" s="19">
+      <c r="E50" s="10">
         <v>4829842</v>
       </c>
-      <c r="F50" s="19">
+      <c r="F50" s="10">
         <v>2613496</v>
       </c>
-      <c r="G50" s="19">
+      <c r="G50" s="10">
         <v>54.111418</v>
       </c>
-      <c r="H50" s="19">
+      <c r="H50" s="10">
         <v>2216346</v>
       </c>
-      <c r="I50" s="19">
+      <c r="I50" s="10">
         <v>45.888582</v>
       </c>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B51" s="18" t="s">
+      <c r="B51" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="18" t="s">
+      <c r="C51" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="D51" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E51" s="19">
+      <c r="E51" s="10">
         <v>3399855</v>
       </c>
-      <c r="F51" s="19">
+      <c r="F51" s="10">
         <v>1838237</v>
       </c>
-      <c r="G51" s="19">
+      <c r="G51" s="10">
         <v>54.068100000000001</v>
       </c>
-      <c r="H51" s="19">
+      <c r="H51" s="10">
         <v>1561618</v>
       </c>
-      <c r="I51" s="19">
+      <c r="I51" s="10">
         <v>45.931899999999999</v>
       </c>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E52" s="17">
+      <c r="E52" s="8">
         <v>4964838</v>
       </c>
-      <c r="F52" s="17">
+      <c r="F52" s="8">
         <v>2784501</v>
       </c>
-      <c r="G52" s="17">
+      <c r="G52" s="8">
         <v>56.084428000000003</v>
       </c>
-      <c r="H52" s="17">
+      <c r="H52" s="8">
         <v>2180337</v>
       </c>
-      <c r="I52" s="17">
+      <c r="I52" s="8">
         <v>43.915571999999997</v>
       </c>
     </row>
     <row r="53" spans="2:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
     </row>
     <row r="54" spans="2:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="56" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B106" s="14" t="s">
+      <c r="B106" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C106" s="15" t="s">
+      <c r="C106" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D106" s="15" t="s">
+      <c r="D106" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E106" s="16" t="s">
+      <c r="E106" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F106" s="14" t="s">
+      <c r="F106" s="5" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1845,16 +1846,16 @@
       <c r="B107" t="s">
         <v>36</v>
       </c>
-      <c r="C107" s="20" t="s">
+      <c r="C107" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D107" s="20" t="s">
+      <c r="D107" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E107" s="20" t="s">
+      <c r="E107" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F107" s="20" t="s">
+      <c r="F107" s="11" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1862,16 +1863,16 @@
       <c r="B108" t="s">
         <v>44</v>
       </c>
-      <c r="C108" s="20" t="s">
+      <c r="C108" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D108" s="20" t="s">
+      <c r="D108" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E108" s="20" t="s">
+      <c r="E108" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F108" s="20" t="s">
+      <c r="F108" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1879,254 +1880,254 @@
       <c r="B109" t="s">
         <v>49</v>
       </c>
-      <c r="C109" s="20" t="s">
+      <c r="C109" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D109" s="20" t="s">
+      <c r="D109" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E109" s="20" t="s">
+      <c r="E109" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="F109" s="20" t="s">
+      <c r="F109" s="11" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B110" s="18" t="s">
+      <c r="B110" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C110" s="21" t="s">
+      <c r="C110" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D110" s="21" t="s">
+      <c r="D110" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E110" s="21" t="s">
+      <c r="E110" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F110" s="21" t="s">
+      <c r="F110" s="12" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B111" s="18" t="s">
+      <c r="B111" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C111" s="21" t="s">
+      <c r="C111" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D111" s="21" t="s">
+      <c r="D111" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E111" s="21" t="s">
+      <c r="E111" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F111" s="21" t="s">
+      <c r="F111" s="12" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B112" s="18" t="s">
+      <c r="B112" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C112" s="21" t="s">
+      <c r="C112" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D112" s="21" t="s">
+      <c r="D112" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E112" s="21" t="s">
+      <c r="E112" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F112" s="21" t="s">
+      <c r="F112" s="12" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B113" s="18" t="s">
+      <c r="B113" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C113" s="21" t="s">
+      <c r="C113" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D113" s="21" t="s">
+      <c r="D113" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E113" s="21" t="s">
+      <c r="E113" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F113" s="21" t="s">
+      <c r="F113" s="12" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B114" s="18" t="s">
+      <c r="B114" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C114" s="21" t="s">
+      <c r="C114" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D114" s="21" t="s">
+      <c r="D114" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E114" s="21" t="s">
+      <c r="E114" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="F114" s="21" t="s">
+      <c r="F114" s="12" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B115" s="18" t="s">
+      <c r="B115" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C115" s="21" t="s">
+      <c r="C115" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="D115" s="21" t="s">
+      <c r="D115" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E115" s="21" t="s">
+      <c r="E115" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="F115" s="21" t="s">
+      <c r="F115" s="12" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B116" s="18" t="s">
+      <c r="B116" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C116" s="21" t="s">
+      <c r="C116" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D116" s="21" t="s">
+      <c r="D116" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E116" s="21" t="s">
+      <c r="E116" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F116" s="21" t="s">
+      <c r="F116" s="12" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B117" s="18" t="s">
+      <c r="B117" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C117" s="21" t="s">
+      <c r="C117" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D117" s="21" t="s">
+      <c r="D117" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="E117" s="21" t="s">
+      <c r="E117" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F117" s="21" t="s">
+      <c r="F117" s="12" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B118" s="18" t="s">
+      <c r="B118" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C118" s="21" t="s">
+      <c r="C118" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D118" s="21" t="s">
+      <c r="D118" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E118" s="21" t="s">
+      <c r="E118" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="F118" s="21" t="s">
+      <c r="F118" s="12" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B119" s="18" t="s">
+      <c r="B119" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C119" s="21" t="s">
+      <c r="C119" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="D119" s="21" t="s">
+      <c r="D119" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="E119" s="21" t="s">
+      <c r="E119" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="F119" s="21" t="s">
+      <c r="F119" s="12" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B120" s="18" t="s">
+      <c r="B120" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C120" s="21" t="s">
+      <c r="C120" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D120" s="21" t="s">
+      <c r="D120" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E120" s="21" t="s">
+      <c r="E120" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F120" s="21" t="s">
+      <c r="F120" s="12" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B121" s="18" t="s">
+      <c r="B121" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C121" s="21" t="s">
+      <c r="C121" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D121" s="21" t="s">
+      <c r="D121" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="E121" s="21" t="s">
+      <c r="E121" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="F121" s="21" t="s">
+      <c r="F121" s="12" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B122" s="18" t="s">
+      <c r="B122" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C122" s="21" t="s">
+      <c r="C122" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="D122" s="21" t="s">
+      <c r="D122" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E122" s="21" t="s">
+      <c r="E122" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F122" s="21" t="s">
+      <c r="F122" s="12" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B123" s="18" t="s">
+      <c r="B123" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C123" s="21" t="s">
+      <c r="C123" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D123" s="21" t="s">
+      <c r="D123" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E123" s="21" t="s">
+      <c r="E123" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F123" s="21" t="s">
+      <c r="F123" s="12" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2134,16 +2135,16 @@
       <c r="B124" t="s">
         <v>99</v>
       </c>
-      <c r="C124" s="20" t="s">
+      <c r="C124" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D124" s="20" t="s">
+      <c r="D124" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E124" s="20" t="s">
+      <c r="E124" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="F124" s="20" t="s">
+      <c r="F124" s="11" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2151,16 +2152,16 @@
       <c r="B125" t="s">
         <v>103</v>
       </c>
-      <c r="C125" s="20" t="s">
+      <c r="C125" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D125" s="20" t="s">
+      <c r="D125" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E125" s="20" t="s">
+      <c r="E125" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="F125" s="20" t="s">
+      <c r="F125" s="11" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2168,16 +2169,16 @@
       <c r="B126" t="s">
         <v>107</v>
       </c>
-      <c r="C126" s="20" t="s">
+      <c r="C126" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="D126" s="20" t="s">
+      <c r="D126" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="E126" s="20" t="s">
+      <c r="E126" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="F126" s="20" t="s">
+      <c r="F126" s="11" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2185,16 +2186,16 @@
       <c r="B127" t="s">
         <v>39</v>
       </c>
-      <c r="C127" s="20" t="s">
+      <c r="C127" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D127" s="20" t="s">
+      <c r="D127" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E127" s="20" t="s">
+      <c r="E127" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="F127" s="20" t="s">
+      <c r="F127" s="11" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2218,7 +2219,25 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBDC9C6B-B1E7-4DE7-B93C-636529D2908A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009C0B5EB41D98674C8F492B58287E64DE" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="7ec16afc8301721c8ec224615f1a29ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9b01763d-3e4a-4b14-b444-60e9c301c4d5" xmlns:ns3="ec1d2b11-2972-412b-988a-b8b45ab29cc1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a31de9878d0b753078abed7561bf22d1" ns2:_="" ns3:_="">
     <xsd:import namespace="9b01763d-3e4a-4b14-b444-60e9c301c4d5"/>
@@ -2405,15 +2424,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2427,13 +2437,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5F23BCA-A17A-47B5-AAA4-800B0FDD8625}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C30A3D06-D2BF-4FBF-AE09-EA382A9C3F7A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C30A3D06-D2BF-4FBF-AE09-EA382A9C3F7A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5F23BCA-A17A-47B5-AAA4-800B0FDD8625}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9b01763d-3e4a-4b14-b444-60e9c301c4d5"/>
+    <ds:schemaRef ds:uri="ec1d2b11-2972-412b-988a-b8b45ab29cc1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1772415D-38A2-4594-8722-BC1E56E3A614}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1772415D-38A2-4594-8722-BC1E56E3A614}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9b01763d-3e4a-4b14-b444-60e9c301c4d5"/>
+    <ds:schemaRef ds:uri="ec1d2b11-2972-412b-988a-b8b45ab29cc1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>